--- a/artfynd/A 29245-2020 artfynd.xlsx
+++ b/artfynd/A 29245-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29245-2020 artfynd.xlsx
+++ b/artfynd/A 29245-2020 artfynd.xlsx
@@ -2985,7 +2985,7 @@
         <v>106951237</v>
       </c>
       <c r="B22" t="n">
-        <v>56502</v>
+        <v>56503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 29245-2020 artfynd.xlsx
+++ b/artfynd/A 29245-2020 artfynd.xlsx
@@ -2871,7 +2871,7 @@
         <v>117194169</v>
       </c>
       <c r="B21" t="n">
-        <v>57283</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
